--- a/research/traditional_assets/database/data/bahrain/bahrain_entertainment.xlsx
+++ b/research/traditional_assets/database/data/bahrain/bahrain_entertainment.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.229</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.494</v>
+        <v>-0.161</v>
       </c>
       <c r="G2">
-        <v>-0.1666666666666667</v>
+        <v>-0.09640287769784173</v>
       </c>
       <c r="H2">
-        <v>-0.1666666666666667</v>
+        <v>-0.09640287769784173</v>
       </c>
       <c r="I2">
-        <v>-0.2265151515151515</v>
+        <v>-0.2575539568345324</v>
       </c>
       <c r="J2">
-        <v>-0.2265151515151515</v>
+        <v>-0.2575539568345324</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="L2">
-        <v>0.2537878787878788</v>
+        <v>0.2467625899280576</v>
       </c>
       <c r="M2">
-        <v>2.97</v>
+        <v>3.212</v>
       </c>
       <c r="N2">
-        <v>0.04236804564907276</v>
+        <v>0.06398406374501991</v>
       </c>
       <c r="O2">
-        <v>0.8865671641791045</v>
+        <v>0.9364431486880467</v>
       </c>
       <c r="P2">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="Q2">
-        <v>0.04236804564907276</v>
+        <v>0.06254980079681274</v>
       </c>
       <c r="R2">
-        <v>0.8865671641791045</v>
+        <v>0.9154518950437318</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.07200000000000006</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.02241594022415942</v>
       </c>
       <c r="U2">
-        <v>0.848</v>
+        <v>0.571</v>
       </c>
       <c r="V2">
-        <v>0.01209700427960057</v>
+        <v>0.01137450199203187</v>
       </c>
       <c r="W2">
-        <v>0.02140575079872204</v>
+        <v>0.0219029374201788</v>
       </c>
       <c r="X2">
-        <v>0.3348744990904548</v>
+        <v>0.2835613868532985</v>
       </c>
       <c r="Y2">
-        <v>-0.3134687482917328</v>
+        <v>-0.2616584494331197</v>
       </c>
       <c r="Z2">
-        <v>0.07386681589255736</v>
+        <v>0.06697116867098367</v>
       </c>
       <c r="AA2">
-        <v>-0.01673195299384444</v>
+        <v>-0.01724868948504471</v>
       </c>
       <c r="AB2">
-        <v>0.2461589617072391</v>
+        <v>0.2028692890880693</v>
       </c>
       <c r="AC2">
-        <v>-0.2628909147010835</v>
+        <v>-0.220117978573114</v>
       </c>
       <c r="AD2">
-        <v>51.8</v>
+        <v>45.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>51.8</v>
+        <v>45.3</v>
       </c>
       <c r="AG2">
-        <v>50.952</v>
+        <v>44.729</v>
       </c>
       <c r="AH2">
-        <v>0.4249384741591469</v>
+        <v>0.4743455497382199</v>
       </c>
       <c r="AI2">
-        <v>0.2485604606525912</v>
+        <v>0.2240356083086053</v>
       </c>
       <c r="AJ2">
-        <v>0.4209100221392459</v>
+        <v>0.4711837267852816</v>
       </c>
       <c r="AK2">
-        <v>0.2454902867715079</v>
+        <v>0.221838128443825</v>
       </c>
       <c r="AL2">
-        <v>0.49</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AM2">
-        <v>-5.69</v>
+        <v>-7.072</v>
       </c>
       <c r="AN2">
-        <v>-40.15503875968992</v>
+        <v>-31.67832167832168</v>
       </c>
       <c r="AO2">
-        <v>-6.102040816326531</v>
+        <v>-5.203488372093024</v>
       </c>
       <c r="AP2">
-        <v>-39.49767441860465</v>
+        <v>-31.27902097902098</v>
       </c>
       <c r="AQ2">
-        <v>0.5254833040421794</v>
+        <v>0.5062217194570136</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.229</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.494</v>
+        <v>-0.161</v>
       </c>
       <c r="G3">
-        <v>-0.1666666666666667</v>
+        <v>-0.09640287769784173</v>
       </c>
       <c r="H3">
-        <v>-0.1666666666666667</v>
+        <v>-0.09640287769784173</v>
       </c>
       <c r="I3">
-        <v>-0.2265151515151515</v>
+        <v>-0.2575539568345324</v>
       </c>
       <c r="J3">
-        <v>-0.2265151515151515</v>
+        <v>-0.2575539568345324</v>
       </c>
       <c r="K3">
-        <v>3.35</v>
+        <v>3.43</v>
       </c>
       <c r="L3">
-        <v>0.2537878787878788</v>
+        <v>0.2467625899280576</v>
       </c>
       <c r="M3">
-        <v>2.97</v>
+        <v>3.212</v>
       </c>
       <c r="N3">
-        <v>0.04236804564907276</v>
+        <v>0.06398406374501991</v>
       </c>
       <c r="O3">
-        <v>0.8865671641791045</v>
+        <v>0.9364431486880467</v>
       </c>
       <c r="P3">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="Q3">
-        <v>0.04236804564907276</v>
+        <v>0.06254980079681274</v>
       </c>
       <c r="R3">
-        <v>0.8865671641791045</v>
+        <v>0.9154518950437318</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.07200000000000006</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.02241594022415942</v>
       </c>
       <c r="U3">
-        <v>0.848</v>
+        <v>0.571</v>
       </c>
       <c r="V3">
-        <v>0.01209700427960057</v>
+        <v>0.01137450199203187</v>
       </c>
       <c r="W3">
-        <v>0.02140575079872204</v>
+        <v>0.0219029374201788</v>
       </c>
       <c r="X3">
-        <v>0.3348744990904548</v>
+        <v>0.2835613868532985</v>
       </c>
       <c r="Y3">
-        <v>-0.3134687482917328</v>
+        <v>-0.2616584494331197</v>
       </c>
       <c r="Z3">
-        <v>0.07386681589255736</v>
+        <v>0.06697116867098367</v>
       </c>
       <c r="AA3">
-        <v>-0.01673195299384444</v>
+        <v>-0.01724868948504471</v>
       </c>
       <c r="AB3">
-        <v>0.2461589617072391</v>
+        <v>0.2028692890880693</v>
       </c>
       <c r="AC3">
-        <v>-0.2628909147010835</v>
+        <v>-0.220117978573114</v>
       </c>
       <c r="AD3">
-        <v>51.8</v>
+        <v>45.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>51.8</v>
+        <v>45.3</v>
       </c>
       <c r="AG3">
-        <v>50.952</v>
+        <v>44.729</v>
       </c>
       <c r="AH3">
-        <v>0.4249384741591469</v>
+        <v>0.4743455497382199</v>
       </c>
       <c r="AI3">
-        <v>0.2485604606525912</v>
+        <v>0.2240356083086053</v>
       </c>
       <c r="AJ3">
-        <v>0.4209100221392459</v>
+        <v>0.4711837267852816</v>
       </c>
       <c r="AK3">
-        <v>0.2454902867715079</v>
+        <v>0.221838128443825</v>
       </c>
       <c r="AL3">
-        <v>0.49</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AM3">
-        <v>-5.69</v>
+        <v>-7.072</v>
       </c>
       <c r="AN3">
-        <v>-40.15503875968992</v>
+        <v>-31.67832167832168</v>
       </c>
       <c r="AO3">
-        <v>-6.102040816326531</v>
+        <v>-5.203488372093024</v>
       </c>
       <c r="AP3">
-        <v>-39.49767441860465</v>
+        <v>-31.27902097902098</v>
       </c>
       <c r="AQ3">
-        <v>0.5254833040421794</v>
+        <v>0.5062217194570136</v>
       </c>
     </row>
   </sheetData>
